--- a/data/inst_9_dia_3.xlsx
+++ b/data/inst_9_dia_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flexible-vrp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFG\Flexible\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F588E33B-0F83-498B-929E-FAA03C89EE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4A2992-6130-442D-BF24-CD3A8E723EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -256,9 +256,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -296,7 +296,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -402,7 +402,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -544,7 +544,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -553,12 +553,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -574,7 +574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -598,7 +598,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -606,7 +606,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -614,7 +614,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -622,7 +622,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -630,7 +630,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -638,7 +638,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,23 +647,24 @@
         <v>17.857142857142858</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <f>SUM(comp_quantity_inst1!C2:C20)</f>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -680,12 +681,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -696,7 +697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -707,7 +708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -718,7 +719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -729,7 +730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -740,7 +741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -751,7 +752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -762,7 +763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -773,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -784,7 +785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -795,7 +796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -806,7 +807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -817,7 +818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -828,7 +829,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -839,7 +840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -850,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -861,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -872,7 +873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -883,7 +884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -894,7 +895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -905,7 +906,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -916,7 +917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -927,7 +928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -938,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -949,7 +950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -960,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -971,7 +972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -982,7 +983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -993,7 +994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1004,7 +1005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1015,7 +1016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1026,7 +1027,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1037,7 +1038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1048,7 +1049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -1070,7 +1071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1081,7 +1082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1103,7 +1104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -1114,7 +1115,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -1125,7 +1126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -1147,7 +1148,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1158,7 +1159,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1169,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -1191,7 +1192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -1202,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -1224,7 +1225,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -1235,7 +1236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1257,7 +1258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1279,7 +1280,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1302,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1321,9 +1322,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1337,7 +1338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1365,7 +1366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1393,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1407,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1421,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1463,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1477,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1533,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1561,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1589,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1673,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1687,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1743,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1785,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
